--- a/src/main/kotlin/com/kcvn/spm/assets/template/ImportTape.xlsx
+++ b/src/main/kotlin/com/kcvn/spm/assets/template/ImportTape.xlsx
@@ -14,7 +14,7 @@
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>Tên sản phẩm</t>
   </si>
@@ -36,6 +36,9 @@
   </si>
   <si>
     <t>Đơn giá</t>
+  </si>
+  <si>
+    <t>Loại xuất hàng</t>
   </si>
 </sst>
 </file>
@@ -389,46 +392,50 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AMI1"/>
+  <dimension ref="A1:AMJ1"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.42578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="18.28515625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="22.140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.85546875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="18.42578125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="19.85546875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="17.42578125" style="1" customWidth="1"/>
-    <col min="8" max="9" width="14.5703125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" customWidth="1"/>
-    <col min="11" max="12" width="15" style="1" customWidth="1"/>
-    <col min="13" max="13" width="16" style="1" customWidth="1"/>
-    <col min="14" max="14" width="17.85546875" style="1" customWidth="1"/>
-    <col min="15" max="15" width="16.7109375" style="1" customWidth="1"/>
-    <col min="16" max="16" width="11.140625" style="1" customWidth="1"/>
-    <col min="17" max="17" width="10" style="1" customWidth="1"/>
-    <col min="18" max="18" width="11" style="1" customWidth="1"/>
-    <col min="19" max="19" width="11.7109375" style="1" customWidth="1"/>
-    <col min="20" max="1023" width="9.140625" style="1"/>
+    <col min="2" max="2" width="23" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18.28515625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="22.140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="15.85546875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="19.85546875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="17.42578125" style="1" customWidth="1"/>
+    <col min="9" max="10" width="14.5703125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" customWidth="1"/>
+    <col min="12" max="13" width="15" style="1" customWidth="1"/>
+    <col min="14" max="14" width="16" style="1" customWidth="1"/>
+    <col min="15" max="15" width="17.85546875" style="1" customWidth="1"/>
+    <col min="16" max="16" width="16.7109375" style="1" customWidth="1"/>
+    <col min="17" max="17" width="11.140625" style="1" customWidth="1"/>
+    <col min="18" max="18" width="10" style="1" customWidth="1"/>
+    <col min="19" max="19" width="11" style="1" customWidth="1"/>
+    <col min="20" max="20" width="11.7109375" style="1" customWidth="1"/>
+    <col min="21" max="1024" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1023" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1024" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="AMF1"/>
       <c r="AMG1"/>
       <c r="AMH1"/>
       <c r="AMI1"/>
+      <c r="AMJ1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
